--- a/output/lmm_early.xlsx
+++ b/output/lmm_early.xlsx
@@ -579,7 +579,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22.571</v>
+        <v>11.86</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -588,7 +588,7 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.138</v>
+        <v>0.204</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -597,7 +597,7 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>1.944</v>
+        <v>2.987</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -606,16 +606,16 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.008</v>
+        <v>0.035</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>0.035</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>0.15125</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.247</v>
+        <v>1.925</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -640,7 +640,7 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0.023</v>
+        <v>0.043</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -649,7 +649,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1.447</v>
+        <v>1.95</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -658,16 +658,16 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.003</v>
+        <v>0.024</v>
       </c>
       <c r="L5" t="n">
-        <v>0.082</v>
+        <v>0.066</v>
       </c>
       <c r="M5" t="n">
-        <v>0.082</v>
+        <v>0.15125</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10.285</v>
+        <v>5.015</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -692,7 +692,7 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0.064</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -701,7 +701,7 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>1.737</v>
+        <v>2.178</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -710,16 +710,16 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.007</v>
+        <v>0.022</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.121</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>0.15125</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>0.008</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.645</v>
+        <v>1.034</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -744,7 +744,7 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0.024</v>
+        <v>0.028</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -753,7 +753,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>1.427</v>
+        <v>1.753</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -762,16 +762,16 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.004</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02</v>
+        <v>0.539</v>
       </c>
       <c r="M7" t="n">
-        <v>0.025</v>
+        <v>0.539</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.639</v>
+        <v>2.942</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -796,16 +796,16 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0.016</v>
+        <v>0.027</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>0.024</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>0.024</v>
       </c>
       <c r="H8" t="n">
-        <v>2.428</v>
+        <v>2.627</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -814,22 +814,22 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.008</v>
+        <v>0.022</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001</v>
+        <v>0.11</v>
       </c>
       <c r="M8" t="n">
-        <v>0.002</v>
+        <v>0.15125</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.003</v>
       </c>
     </row>
   </sheetData>
